--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N47_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.27210712643139</v>
+        <v>6.544217408045101</v>
       </c>
       <c r="D2" t="n">
-        <v>39.77006546315118</v>
+        <v>6.462635637762068</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
